--- a/Documents/devfiles/excel/HR JO sample date DBOX MSForms.xlsx
+++ b/Documents/devfiles/excel/HR JO sample date DBOX MSForms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitedlaboratoriesinc-my.sharepoint.com/personal/c_cadiaz_unilab_com_ph/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7725311C-877B-4BAD-BE8E-5194624766CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26195C8-B57C-412B-81E4-6ADDB2CF44F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="660" windowWidth="20730" windowHeight="11040" xr2:uid="{95289839-A40E-4980-8664-A8D6436BA279}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95289839-A40E-4980-8664-A8D6436BA279}"/>
   </bookViews>
   <sheets>
     <sheet name="HR JO Response" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -642,33 +642,6 @@
   </si>
   <si>
     <t>Retirement Benefit • Marriage Bonus • Baby Bonus • Funeral Assistance</t>
-  </si>
-  <si>
-    <t>Rico Roller Coaster</t>
-  </si>
-  <si>
-    <t>Nina Nagaraya</t>
-  </si>
-  <si>
-    <t>Marco Mang Juan</t>
-  </si>
-  <si>
-    <t>Joy Chippy</t>
-  </si>
-  <si>
-    <t>Grace Green Peas</t>
-  </si>
-  <si>
-    <t>Tina Tostillas</t>
-  </si>
-  <si>
-    <t>Joey Oishi</t>
-  </si>
-  <si>
-    <t>Candy Calbee</t>
-  </si>
-  <si>
-    <t>Archie Choco Mucho</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08F5028-956B-4C5B-88AE-8948E0E68902}">
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
@@ -2506,51 +2479,6 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="H13" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="H14" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="H15" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
-      <c r="H16" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H17" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H18" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H19" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H20" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H21" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
